--- a/docs/LabPulse Sensors.xlsx
+++ b/docs/LabPulse Sensors.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LabPulse Tommy\LabPulse\docker_refactor\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LabPulse Tommy\LabPulse\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDECCE7B-8D60-4D83-92E9-3E72C4E1EFB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C40D92EF-10DD-472F-9F6B-CAC7030914CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{BEA7CCE9-7876-423F-8F4B-DF57CA569CE3}"/>
   </bookViews>
@@ -128,7 +128,7 @@
     <t>Present - 0 Reading</t>
   </si>
   <si>
-    <t>UPS Hat (ITS NOT THIS)</t>
+    <t>UPS Hat (Now correct)</t>
   </si>
 </sst>
 </file>
@@ -773,7 +773,7 @@
     <hyperlink ref="A3" r:id="rId3" xr:uid="{C513B426-BB3D-4ABF-89F3-FB01FBBF1EF7}"/>
     <hyperlink ref="A4" r:id="rId4" xr:uid="{CAC0849B-33AA-402F-98D2-BFBB8AF0417E}"/>
     <hyperlink ref="A10" r:id="rId5" xr:uid="{06AD4B34-F348-42CD-9811-25DD6FE397E7}"/>
-    <hyperlink ref="A9" r:id="rId6" display="UPS Hat" xr:uid="{55BB8C77-91EB-49B6-BB4A-9A01D369BDE7}"/>
+    <hyperlink ref="A9" r:id="rId6" xr:uid="{55BB8C77-91EB-49B6-BB4A-9A01D369BDE7}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
